--- a/data2026-08-05.xlsx
+++ b/data2026-08-05.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Crypto Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crypto Results'!$A$1:$H$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crypto Results'!$A$1:$L$201</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -10571,7 +10571,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H201"/>
+  <autoFilter ref="A1:L201"/>
   <conditionalFormatting sqref="E2:E201">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>70</formula>
